--- a/assignments/lab5/TestPlan.xlsx
+++ b/assignments/lab5/TestPlan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\sachxna\2sem\swe\swe-lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\sachxna\2sem\swe\swe-lab\assignments\lab5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59345387-E196-45A4-89AD-0716EF53D356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D11579-EE11-4014-A9DD-CB6278BBE4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Project Name</t>
   </si>
@@ -68,39 +68,6 @@
   </si>
   <si>
     <t>Pass?</t>
-  </si>
-  <si>
-    <t>Logging in</t>
-  </si>
-  <si>
-    <t>Should get to home screen</t>
-  </si>
-  <si>
-    <t>User directed to different page</t>
-  </si>
-  <si>
-    <t>Signing up for webinar</t>
-  </si>
-  <si>
-    <t>Get confirmation email</t>
-  </si>
-  <si>
-    <t>Confirmation email received</t>
-  </si>
-  <si>
-    <t>Click magnifying glass</t>
-  </si>
-  <si>
-    <t>Text changes sizes</t>
-  </si>
-  <si>
-    <t>Whole page gets bigger</t>
-  </si>
-  <si>
-    <t>Go to blog post</t>
-  </si>
-  <si>
-    <t>Click blog post hero image</t>
   </si>
 </sst>
 </file>
@@ -503,7 +470,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FAEC6DB-C357-8477-8DB3-E4749AC3A435}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -570,7 +537,7 @@
                   <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B675B9AD-1822-1F75-2814-4067E15064F4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -637,7 +604,7 @@
                   <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E3DC0B4-3ADF-3091-FB3B-B25CDC9815E7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -704,7 +671,7 @@
                   <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8008FDEF-7CC1-94D5-6591-DD18BC73C412}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -771,7 +738,7 @@
                   <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21BD0F5C-4A9A-E592-532F-2178071061E2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -838,7 +805,7 @@
                   <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D866B215-DEDA-2EBC-0B86-15D29F26405B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -905,7 +872,7 @@
                   <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3E0D225-BE9A-AFBC-F8BB-B5EDB799212C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -972,7 +939,7 @@
                   <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D141EBC-0D2B-1851-CCD0-18ACF433A148}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1039,7 +1006,7 @@
                   <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50E99FDC-0FE0-174A-973F-F2AB6282146F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1106,7 +1073,7 @@
                   <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76F68330-D663-D976-8733-C55417EA733E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1173,7 +1140,7 @@
                   <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{792C9355-B137-0533-3307-77250F40358B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1240,7 +1207,7 @@
                   <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAC9FD15-C57D-FF9A-3F6A-E2A0E33D03DC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1307,7 +1274,7 @@
                   <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEBBC5C9-B19A-F5FF-1772-C06F4D305A8F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1374,7 +1341,7 @@
                   <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F029D764-6C95-D680-4EC6-B7BE73415330}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1441,7 +1408,7 @@
                   <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{355D380B-257E-F341-E888-30D5CD3D8370}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1898,75 +1865,35 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="8">
-        <v>42435</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="8">
-        <v>42441</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="8">
-        <v>42449</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" s="8">
-        <v>42461</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
